--- a/DateBase/orders/Dang Nguyen48_2026-8-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-13.xlsx
@@ -777,6 +777,9 @@
       <c r="C41" t="str">
         <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -835,7 +838,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0305555151051810661561110515101015151051051055555101510301010100</v>
+        <v>03055551510518106615611105151010151510510510555551015103010101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-8-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-13.xlsx
@@ -840,6 +840,9 @@
       <c r="G2" t="str">
         <v>03055551510518106615611105151010151510510510555551015103010101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
